--- a/Outros Formatos/Pio.ContrYgra.xlsx
+++ b/Outros Formatos/Pio.ContrYgra.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Outros Formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C0F56C-A555-443D-ABA3-D9195483F74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AAF496-CAD9-4A89-8899-602E5D693DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2F3F7680-5153-4029-AED4-DC87BFED0C66}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pio.BantBlink" sheetId="1" r:id="rId1"/>
+    <sheet name="Pio.GolgYgra" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="33">
   <si>
     <t>Função</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Terreno</t>
   </si>
   <si>
-    <t>Mana</t>
-  </si>
-  <si>
     <t>Draw</t>
   </si>
   <si>
@@ -71,10 +68,73 @@
     <t>Control</t>
   </si>
   <si>
-    <t>Anule</t>
-  </si>
-  <si>
-    <t>Blink</t>
+    <t>Cauldron Familiar </t>
+  </si>
+  <si>
+    <t>Gilded Goose </t>
+  </si>
+  <si>
+    <t>Ygra, Eater of All </t>
+  </si>
+  <si>
+    <t>Badgermole Cub </t>
+  </si>
+  <si>
+    <t>Witch's Oven </t>
+  </si>
+  <si>
+    <t>Abrupt Decay </t>
+  </si>
+  <si>
+    <t>Cache Grab </t>
+  </si>
+  <si>
+    <t>Fatal Push </t>
+  </si>
+  <si>
+    <t>Witherbloom Charm </t>
+  </si>
+  <si>
+    <t>Traverse the Ulvenwald </t>
+  </si>
+  <si>
+    <t>Scavenger's Talent </t>
+  </si>
+  <si>
+    <t>Dredger's Insight </t>
+  </si>
+  <si>
+    <t>The Meathook Massacre </t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Combo</t>
+  </si>
+  <si>
+    <t>Darkbore Pathway</t>
+  </si>
+  <si>
+    <t>Boseiju, Who Endures</t>
+  </si>
+  <si>
+    <t>Swamp </t>
+  </si>
+  <si>
+    <t>Fountainport </t>
+  </si>
+  <si>
+    <t>Blooming Marsh </t>
+  </si>
+  <si>
+    <t>Forest </t>
+  </si>
+  <si>
+    <t>Overgrown Tomb </t>
   </si>
 </sst>
 </file>
@@ -494,7 +554,10 @@
       </c>
       <c r="B2" t="b">
         <f>C2&lt;&gt;D2</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -503,7 +566,10 @@
       </c>
       <c r="B3" t="b">
         <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -512,7 +578,10 @@
       </c>
       <c r="B4" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,7 +590,10 @@
       </c>
       <c r="B5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -530,7 +602,10 @@
       </c>
       <c r="B6" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -539,7 +614,10 @@
       </c>
       <c r="B7" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -548,7 +626,10 @@
       </c>
       <c r="B8" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -557,7 +638,10 @@
       </c>
       <c r="B9" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -566,7 +650,10 @@
       </c>
       <c r="B10" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -575,7 +662,10 @@
       </c>
       <c r="B11" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,7 +674,10 @@
       </c>
       <c r="B12" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -593,7 +686,10 @@
       </c>
       <c r="B13" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -602,7 +698,10 @@
       </c>
       <c r="B14" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -611,7 +710,10 @@
       </c>
       <c r="B15" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -620,435 +722,576 @@
       </c>
       <c r="B16" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
       <c r="B18" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
       <c r="B19" t="b">
         <f>C19&lt;&gt;D19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B20" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B21" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B22" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B23" t="b">
-        <f>C23&lt;&gt;D23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B24" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <f>C24&lt;&gt;D24</f>
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B25" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <f>C25&lt;&gt;D25</f>
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B26" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <f>C26&lt;&gt;D26</f>
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B27" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B28" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B29" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B30" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B31" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B32" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B33" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B34" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B35" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B36" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B37" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B38" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B39" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <f>C39&lt;&gt;D39</f>
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B40" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <f>C40&lt;&gt;D40</f>
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B41" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <f>C41&lt;&gt;D41</f>
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B42" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <f>C42&lt;&gt;D42</f>
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B43" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B44" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B45" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B46" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B47" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <f>C47&lt;&gt;D47</f>
+        <v>1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B48" t="b">
         <f>C48&lt;&gt;D48</f>
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" t="b">
+        <f>C49&lt;&gt;D49</f>
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" t="b">
+        <f>C50&lt;&gt;D50</f>
+        <v>1</v>
+      </c>
+      <c r="D50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" t="b">
+        <f>C51&lt;&gt;D51</f>
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" t="b">
+        <f>C52&lt;&gt;D52</f>
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" t="b">
+        <f>C56&lt;&gt;D56</f>
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" t="b">
+        <f>C57&lt;&gt;D57</f>
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" t="b">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>10</v>
-      </c>
-      <c r="B52" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>11</v>
-      </c>
-      <c r="B55" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>11</v>
-      </c>
-      <c r="B59" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>9</v>
-      </c>
-      <c r="B62" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B64" t="b">
         <f t="shared" si="0"/>
@@ -1057,7 +1300,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65" t="b">
         <f t="shared" si="0"/>
@@ -1066,7 +1309,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B66" t="b">
         <f t="shared" si="0"/>
@@ -1075,7 +1318,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B67" t="b">
         <f t="shared" ref="B67:B76" si="1">C67&lt;&gt;D67</f>
@@ -1084,7 +1327,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B68" t="b">
         <f t="shared" si="1"/>
@@ -1093,7 +1336,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B69" t="b">
         <f t="shared" si="1"/>
@@ -1102,7 +1345,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B70" t="b">
         <f t="shared" si="1"/>
@@ -1111,7 +1354,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B71" t="b">
         <f t="shared" si="1"/>
@@ -1120,7 +1363,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B72" t="b">
         <f t="shared" si="1"/>
@@ -1129,7 +1372,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B73" t="b">
         <f t="shared" si="1"/>
@@ -1138,7 +1381,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B74" t="b">
         <f t="shared" si="1"/>
@@ -1147,7 +1390,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B75" t="b">
         <f t="shared" si="1"/>
@@ -1156,7 +1399,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B76" t="b">
         <f t="shared" si="1"/>
